--- a/数据表/Datas/ThreatLevelConfig_威胁等级配置.xlsx
+++ b/数据表/Datas/ThreatLevelConfig_威胁等级配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -44,7 +44,7 @@
     <t>alertDecayPerSecondMilli</t>
   </si>
   <si>
-    <t>distanceBands</t>
+    <t>*distanceBands</t>
   </si>
   <si>
     <t>##type</t>
@@ -56,7 +56,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>(list#sep=|),AlertDistanceBand#sep=,</t>
+    <t>list,AlertDistanceBand</t>
   </si>
   <si>
     <t>##group</t>
@@ -65,10 +65,22 @@
     <t>c</t>
   </si>
   <si>
+    <t>maxDistanceMilli</t>
+  </si>
+  <si>
+    <t>alertPerSecondMilli</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>威胁等级</t>
     </r>
     <r>
@@ -82,10 +94,24 @@
     </r>
   </si>
   <si>
-    <t>显示名</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>显示名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>最大正面视野距离，千分之一</t>
     </r>
     <r>
@@ -108,28 +134,97 @@
     </r>
   </si>
   <si>
-    <t>脱离视野后每秒降低警惕值</t>
-  </si>
-  <si>
-    <t>由近到远的警惕增长距离段</t>
-  </si>
-  <si>
-    <t>低威胁</t>
-  </si>
-  <si>
-    <t>1000,600|2000,300|3000,150</t>
-  </si>
-  <si>
-    <t>中威胁</t>
-  </si>
-  <si>
-    <t>1500,800|3000,400|5000,200</t>
-  </si>
-  <si>
-    <t>高威胁</t>
-  </si>
-  <si>
-    <t>2000,1000|4000,500|7000,250</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>脱离视野后每秒降低警惕值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>该段最大距离，单位千分之一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Unity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每秒增加警惕值，满值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1000</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>低威胁</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中威胁</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高威胁</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -179,15 +274,160 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Andale Mono"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -196,158 +436,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="PingFang SC Regular"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -404,18 +499,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -565,7 +648,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -577,6 +660,32 @@
       <left style="thin">
         <color rgb="FF9BBB9B"/>
       </left>
+      <right style="thin">
+        <color rgb="FF9BBB9B"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9BBB9B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BBB9B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9BBB9B"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9BBB9B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BBB9B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF9BBB9B"/>
       </right>
@@ -605,6 +714,32 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF9EBDD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9EBDD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9EBDD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9EBDD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9EBDD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9EBDD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
@@ -613,6 +748,19 @@
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
@@ -748,22 +896,31 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -772,46 +929,43 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -823,117 +977,123 @@
     <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1407,153 +1567,286 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.4926470588235" style="2" customWidth="1"/>
     <col min="3" max="3" width="10" style="2" customWidth="1"/>
     <col min="4" max="4" width="26.7132352941176" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28" style="2" customWidth="1"/>
-    <col min="6" max="6" width="46.0735294117647" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="30.1470588235294" style="2" customWidth="1"/>
+    <col min="6" max="6" width="38.9632352941176" style="2" customWidth="1"/>
+    <col min="7" max="7" width="29.4117647058824" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+    <row r="1" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="7"/>
     </row>
-    <row r="2" customHeight="1" spans="1:6">
-      <c r="A2" s="5" t="s">
+    <row r="2" customHeight="1" spans="1:7">
+      <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="G2" s="11"/>
     </row>
-    <row r="3" customHeight="1" spans="1:6">
-      <c r="A3" s="7" t="s">
+    <row r="3" customHeight="1" spans="1:7">
+      <c r="A3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="14" t="s">
         <v>11</v>
       </c>
+      <c r="G3" s="14" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="4" customHeight="1" spans="1:6">
-      <c r="A4" s="9" t="s">
+    <row r="4" customHeight="1" spans="1:7">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="G4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="10" t="s">
+    </row>
+    <row r="5" customHeight="1" spans="1:7">
+      <c r="A5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="B5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="C5" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="D5" s="16" t="s">
         <v>17</v>
       </c>
+      <c r="E5" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" customHeight="1" spans="1:6">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12">
+    <row r="6" customHeight="1" spans="1:7">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="12">
+      <c r="C6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="17">
         <v>3000</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E6" s="17">
         <v>200</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>19</v>
+      <c r="F6" s="17">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="17">
+        <v>600</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:6">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12">
+    <row r="7" customHeight="1" spans="1:7">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17">
+        <v>2000</v>
+      </c>
+      <c r="G7" s="17">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:7">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17">
+        <v>3000</v>
+      </c>
+      <c r="G8" s="17">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:7">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:7">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17">
         <v>2</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="C10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="17">
         <v>5000</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E10" s="17">
         <v>150</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>21</v>
+      <c r="F10" s="17">
+        <v>1500</v>
+      </c>
+      <c r="G10" s="17">
+        <v>800</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:6">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12">
+    <row r="11" customHeight="1" spans="1:7">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17">
+        <v>3000</v>
+      </c>
+      <c r="G11" s="17">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:7">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17">
+        <v>5000</v>
+      </c>
+      <c r="G12" s="17">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:7">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:7">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17">
         <v>3</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="12">
+      <c r="C14" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="17">
         <v>7000</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E14" s="17">
         <v>100</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>23</v>
+      <c r="F14" s="17">
+        <v>2000</v>
+      </c>
+      <c r="G14" s="17">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:7">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17">
+        <v>4000</v>
+      </c>
+      <c r="G15" s="17">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:7">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17">
+        <v>7000</v>
+      </c>
+      <c r="G16" s="17">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/数据表/Datas/ThreatLevelConfig_威胁等级配置.xlsx
+++ b/数据表/Datas/ThreatLevelConfig_威胁等级配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -50,10 +50,13 @@
     <t>##type</t>
   </si>
   <si>
+    <t>EnemyPartyThreatLevel</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <t>list,AlertDistanceBand</t>
@@ -431,13 +434,13 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF202020"/>
+      <color rgb="FF9C0006"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF202020"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
@@ -1045,12 +1048,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1571,274 +1571,274 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.4926470588235" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.6764705882353" style="2" customWidth="1"/>
     <col min="3" max="3" width="10" style="2" customWidth="1"/>
     <col min="4" max="4" width="26.7132352941176" style="2" customWidth="1"/>
     <col min="5" max="5" width="30.1470588235294" style="2" customWidth="1"/>
     <col min="6" max="6" width="38.9632352941176" style="2" customWidth="1"/>
-    <col min="7" max="7" width="29.4117647058824" style="3" customWidth="1"/>
+    <col min="7" max="7" width="29.4117647058824" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" customHeight="1" spans="1:7">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="11"/>
+      <c r="E2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" customHeight="1" spans="1:7">
-      <c r="A3" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>11</v>
+      <c r="B3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:7">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
         <v>13</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:7">
-      <c r="A5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="16" t="s">
+      <c r="A5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="D5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="E5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>20</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:7">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16">
         <v>1</v>
       </c>
-      <c r="C6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="17">
+      <c r="C6" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="16">
         <v>3000</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="16">
         <v>200</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="16">
         <v>1000</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="16">
         <v>600</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:7">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16">
         <v>2000</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="16">
         <v>300</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:7">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16">
         <v>3000</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="16">
         <v>150</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:7">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" customHeight="1" spans="1:7">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16">
         <v>2</v>
       </c>
-      <c r="C10" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="17">
+      <c r="C10" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="16">
         <v>5000</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="16">
         <v>150</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="16">
         <v>1500</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="16">
         <v>800</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:7">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16">
         <v>3000</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="16">
         <v>400</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:7">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16">
         <v>5000</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="16">
         <v>200</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:7">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" customHeight="1" spans="1:7">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16">
         <v>3</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="17">
+      <c r="C14" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="16">
         <v>7000</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="16">
         <v>100</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="16">
         <v>2000</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="16">
         <v>1000</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:7">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16">
         <v>4000</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="16">
         <v>500</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:7">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16">
         <v>7000</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="16">
         <v>250</v>
       </c>
     </row>
